--- a/data/2.full_abstracting/25_12_01_fullabstracting.xlsx
+++ b/data/2.full_abstracting/25_12_01_fullabstracting.xlsx
@@ -1,68 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4C7CFDCE8F79A8D366075C52F355D2F43853E460" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64C05B7E-2022-42ED-A336-7A745F95A370}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>doi</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>journal</t>
-  </si>
-  <si>
-    <t>authors</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>abstract</t>
-  </si>
-  <si>
-    <t>decision</t>
-  </si>
-  <si>
-    <t>rayyan-399527348</t>
-  </si>
-  <si>
-    <t>Daley, Nola and Murano, Dana M. and Walton, Kate E.</t>
-  </si>
-  <si>
-    <t>include</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,25 +59,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -162,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -196,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -231,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -407,51 +350,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>authors</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rayyan-399527348</t>
+        </is>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Daley, Nola and Murano, Dana M. and Walton, Kate E.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Predicting student success: Considering social and emotional skills, growth mindset, and motivation</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>A growing body of evidence has found that social and emotional (SE) skills are positively associated with many school-related outcomes. In recent years, the Big Five personality framework has gained support as an organizing framework for various SE skills. While many prominent taxonomies of SE skills map to the Big Five, several additional models include skills related to motivation and growth mindset that do not align with the Big Five. We examined the extent to which these constructs overlapped with SE skills organized by the Big Five framework and whether they provided incremental validity in predicting school-related outcomes. ACT test takers (N = 1755) from across the United States, mostly from high-income families and predominantly in 11th or 12th grade, completed several measures. These included a measure of SE skills as organized by the Big Five (i.e., BFI-2-S), items on school-related outcomes, measures of motivation (i.e., MSLQ, Expectancy-Value-Cost Scale, Self-Determination Scale), and a measure of growth mindset (i.e., the Growth Mindset Scale). We found that growth mindset and motivation correlated with SE skills as organized by the Big Five. These constructs also helped predict additional variance in school-related outcomes, such as GPA and ACT scores. Given the independent contributions of growth mindset and motivation, incorporating these constructs into school-based assessments, alongside SE skills, could be beneficial in supporting students. Impact Statement: The results from this study suggest that measuring growth mindset and motivation along with social and emotional skills could help to better predict which students are likely to be successful academically. From a theoretical standpoint, the current study suggests the Big Five alone may not fully capture all factors relevant for student success. Â© 2025</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
       </c>
     </row>
   </sheetData>
